--- a/business_forms/029_new_partner_engagement_form--business_forms.xlsx
+++ b/business_forms/029_new_partner_engagement_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'january'}</t>
+          <t>january</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'January'}</t>
+          <t>January</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'february'}</t>
+          <t>february</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'February'}</t>
+          <t>February</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'march'}</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'March'}</t>
+          <t>March</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'april'}</t>
+          <t>april</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'April'}</t>
+          <t>April</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'may'}</t>
+          <t>may</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'May'}</t>
+          <t>May</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'june'}</t>
+          <t>june</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'June'}</t>
+          <t>June</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'july'}</t>
+          <t>july</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'July'}</t>
+          <t>July</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'august'}</t>
+          <t>august</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'August'}</t>
+          <t>August</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'september'}</t>
+          <t>september</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'September'}</t>
+          <t>September</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'october'}</t>
+          <t>october</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'October'}</t>
+          <t>October</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'november'}</t>
+          <t>november</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'November'}</t>
+          <t>November</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'december'}</t>
+          <t>december</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'December'}</t>
+          <t>December</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_2010}</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 2010}</t>
+          <t>2010</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2011}</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2011}</t>
+          <t>2011</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_2012}</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 2012}</t>
+          <t>2012</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_2013}</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 2013}</t>
+          <t>2013</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_2014}</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 2014}</t>
+          <t>2014</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_2015}</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 2015}</t>
+          <t>2015</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_2016}</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 2016}</t>
+          <t>2016</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_2017}</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 2017}</t>
+          <t>2017</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_2018}</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 2018}</t>
+          <t>2018</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_2019}</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 2019}</t>
+          <t>2019</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_2020}</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 2020}</t>
+          <t>2020</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_2021}</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 2021}</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_2022}</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 2022}</t>
+          <t>2022</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_2023}</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 2023}</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_2024}</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 2024}</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_2025}</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': 2025}</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
